--- a/stories/arbres/TREE-AUT-037.xlsx
+++ b/stories/arbres/TREE-AUT-037.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara écoute papa. Sara entend les mots : manteau, sortir, rentrer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2401,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2596,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2705,6 +2763,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2930,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3097,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3264,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3431,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3598,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3765,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3960,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4029,6 +4127,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4294,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4461,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4628,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4677,6 +4795,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4962,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5129,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5191,6 +5324,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5353,6 +5491,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5658,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5825,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5992,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6159,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6326,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6187,7 +6355,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6325,6 +6493,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6679,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6852,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7047,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7025,6 +7214,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7409,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7377,6 +7576,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7743,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7910,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8077,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8244,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8411,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8578,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8539,6 +8773,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8701,6 +8940,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9107,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9274,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9441,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9608,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9775,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9942,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10137,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10025,6 +10304,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10471,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10638,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10805,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10972,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11139,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10859,7 +11168,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10997,6 +11306,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11860,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12027,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11887,6 +12222,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12049,6 +12389,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12556,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12723,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12890,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13057,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13224,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13391,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13211,6 +13586,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13373,6 +13753,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13920,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14087,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14254,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14021,6 +14421,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14588,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14345,6 +14755,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14535,6 +14950,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14697,6 +15117,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15284,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15451,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15618,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15785,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15952,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15542,6 +15992,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-037.xlsx
+++ b/stories/arbres/TREE-AUT-037.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara écoute papa. Sara entend les mots : manteau, sortir, rentrer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2406,6 +2417,7 @@
           <t>narrateur|Sara a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2768,6 +2781,7 @@
           <t>narrateur|Sara rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2935,6 +2949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3102,6 +3117,7 @@
           <t>narrateur|Sara rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3269,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3436,6 +3453,7 @@
           <t>narrateur|Sara rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3603,6 +3621,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3789,7 @@
           <t>narrateur|Sara a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3965,6 +3985,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4132,6 +4153,7 @@
           <t>narrateur|Sara rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4299,6 +4321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4466,6 +4489,7 @@
           <t>narrateur|Sara rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4633,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4800,6 +4825,7 @@
           <t>narrateur|Sara rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4967,6 +4993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5134,6 +5161,7 @@
           <t>narrateur|Sara a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5329,6 +5357,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5496,6 +5525,7 @@
           <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5663,6 +5693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5830,6 +5861,7 @@
           <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5997,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6164,6 +6197,7 @@
           <t>narrateur|Sara rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6331,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6534,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6722,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6857,6 +6894,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7052,6 +7090,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
           <t>narrateur|Sara a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
           <t>narrateur|Sara rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>narrateur|Sara rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>narrateur|Sara rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Sara a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9613,6 +9666,7 @@
           <t>narrateur|Sara rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9780,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9947,6 +10002,7 @@
           <t>narrateur|Sara a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10142,6 +10198,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10309,6 +10366,7 @@
           <t>narrateur|Sara rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10476,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10643,6 +10702,7 @@
           <t>narrateur|Sara rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10810,6 +10870,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10977,6 +11038,7 @@
           <t>narrateur|Sara rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11144,6 +11206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12099,7 @@
           <t>narrateur|Sara a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12227,6 +12295,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12394,6 +12463,7 @@
           <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12799,7 @@
           <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13135,7 @@
           <t>narrateur|Sara rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13471,7 @@
           <t>narrateur|Sara a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13591,6 +13667,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13758,6 +13835,7 @@
           <t>narrateur|Sara rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13925,6 +14003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14092,6 +14171,7 @@
           <t>narrateur|Sara rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14259,6 +14339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14426,6 +14507,7 @@
           <t>narrateur|Sara rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14593,6 +14675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14760,6 +14843,7 @@
           <t>narrateur|Sara a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14955,6 +15039,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15122,6 +15207,7 @@
           <t>narrateur|Sara rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15289,6 +15375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15456,6 +15543,7 @@
           <t>narrateur|Sara rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15623,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15790,6 +15879,7 @@
           <t>narrateur|Sara rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15957,6 +16047,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15975,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15999,6 +16090,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16200,6 +16305,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-037.xlsx
+++ b/stories/arbres/TREE-AUT-037.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prendre son manteau avant de sortir — près de la fenêtre</t>
+          <t>Le manteau jaune près de la gouttière</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un limaçon a laissé un trait d'argent sur la vitre. Sarah prend son manteau jaune avant de sortir, et elle le raccroche en rentrant.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara écoute papa. Sara entend les mots : manteau, sortir, rentrer.</t>
+          <t>La gouttière fait glou, glou. Une goutte tombe sur le carreau. Elle fait un rond brillant. Sur la vitre, un limaçon a passé. Il a laissé un trait d'argent. Le trait brille tout doux. Ça sent le pain grillé. Une miette reste sur la table. Le manteau jaune attend au crochet. Le crochet est froid, tout près. Un bouton argenté brille. Papa essuie la goutte. Il a un torchon bleu. Maman plie une écharpe de laine. La laine est un peu rêche. Dehors, un oiseau se tait. Le village est calme. Tu as vu le limaçon, Sarah ? Oui, papa. Il a brillé. En ce moment, Sarah touche le bouton. Le bouton est lisse et froid. Je veux aller jouer ! D'accord. Avant de sortir, on prend le manteau. En rentrant, on le raccroche. Le manteau, papa. Oui. On le prend. On sort, puis on rentre. Et on le raccroche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,37 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara écoute papa. Sara entend les mots : manteau, sortir, rentrer.</t>
+          <t>narrateur|La gouttière fait glou, glou.
+narrateur|Une goutte tombe sur le carreau.
+narrateur|Elle fait un rond brillant.
+narrateur|Sur la vitre, un limaçon a passé.
+narrateur|Il a laissé un trait d'argent.
+narrateur|Le trait brille tout doux.
+narrateur|Ça sent le pain grillé.
+narrateur|Une miette reste sur la table.
+narrateur|Le manteau jaune attend au crochet.
+narrateur|Le crochet est froid, tout près.
+narrateur|Un bouton argenté brille.
+narrateur|Papa essuie la goutte.
+narrateur|Il a un torchon bleu.
+narrateur|Maman plie une écharpe de laine.
+narrateur|La laine est un peu rêche.
+narrateur|Dehors, un oiseau se tait.
+narrateur|Le village est calme.
+papa|Tu as vu le limaçon, Sarah ?
+enfant-f|Oui, papa.
+enfant-f|Il a brillé.
+narrateur|En ce moment, Sarah touche le bouton.
+narrateur|Le bouton est lisse et froid.
+enfant-f|Je veux aller jouer !
+maman|D'accord.
+papa|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.
+enfant-f|Le manteau, papa.
+papa|Oui.
+papa|On le prend.
+maman|On sort, puis on rentre.
+papa|Et on le raccroche.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Sarah peut jouer à trois endroits. La cuisine, le jardin, ou la chambre ? Tu choisis. Avant de sortir, on prend le manteau.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1563,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Sarah peut jouer à trois endroits.
+papa|La cuisine, le jardin, ou la chambre ?
+maman|Tu choisis.
+maman|Avant de sortir, on prend le manteau.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers la cuisine. Le carrelage est un peu froid. Ça sent encore le pain grillé. Une miette brille sur la table. La porte du jardin est là. Le manteau jaune est sur la chaise. Viens, Sarah. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah glisse un bras, puis l'autre. Le tissu est un peu épais. Bravo. Tu as pris ton manteau. En rentrant, on le raccroche. Sur la chaise ? Oui. À sa place. Une casserole chante tout bas. Sarah touche le bouton argenté.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,8 +1734,24 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Sarah va vers la cuisine.
+narrateur|Le carrelage est un peu froid.
+narrateur|Ça sent encore le pain grillé.
+narrateur|Une miette brille sur la table.
+narrateur|La porte du jardin est là.
+narrateur|Le manteau jaune est sur la chaise.
+papa|Viens, Sarah.
+papa|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah glisse un bras, puis l'autre.
+narrateur|Le tissu est un peu épais.
+maman|Bravo.
+maman|Tu as pris ton manteau.
+papa|En rentrant, on le raccroche.
+enfant-f|Sur la chaise ?
+maman|Oui. À sa place.
+narrateur|Une casserole chante tout bas.
+narrateur|Sarah touche le bouton argenté.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1718,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Sarah est dans la cuisine. Avant de sortir, elle prend quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1939,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Sarah est dans la cuisine.
+maman|Avant de sortir, elle prend quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On prend le manteau, avant de sortir. Le manteau jaune est sur la chaise. Bravo, Sarah. Tu as fait du bon travail. En rentrant, on le raccroche. À sa place. Oui. On continue ensemble ? Oui. La miette brille encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2112,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+narrateur|On prend le manteau, avant de sortir.
+narrateur|Le manteau jaune est sur la chaise.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|En rentrant, on le raccroche.
+enfant-f|À sa place.
+maman|Oui. On continue ensemble ?
+enfant-f|Oui.
+narrateur|La miette brille encore.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2078,7 +2149,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Sarah peut encore jouer, dans la cuisine. Les cubes, le livre, ou la dînette ? Tu choisis. Le manteau attend, tout près.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2246,7 +2317,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Sarah peut encore jouer, dans la cuisine.
+maman|Les cubes, le livre, ou la dînette ?
+papa|Tu choisis.
+papa|Le manteau attend, tout près.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2274,7 +2348,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>Dans la cuisine, les cubes attendent. Ils tapent un peu le carrelage. Toc, toc. Un mur, papa. D'accord. Tout doux. Le manteau jaune reste sur la chaise. Quand on sort, on le prend. En rentrant, on le raccroche. Je m'en souviens. Bravo, Sarah. Sarah pose encore un cube, tout lent. Le carrelage est froid sous le pied. Tu as fini ce jeu ? Encore un peu. D'accord. Puis le manteau.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2414,7 +2488,21 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, les cubes attendent.
+narrateur|Ils tapent un peu le carrelage.
+narrateur|Toc, toc.
+enfant-f|Un mur, papa.
+papa|D'accord. Tout doux.
+narrateur|Le manteau jaune reste sur la chaise.
+papa|Quand on sort, on le prend.
+maman|En rentrant, on le raccroche.
+enfant-f|Je m'en souviens.
+papa|Bravo, Sarah.
+narrateur|Sarah pose encore un cube, tout lent.
+narrateur|Le carrelage est froid sous le pied.
+maman|Tu as fini ce jeu ?
+enfant-f|Encore un peu.
+papa|D'accord. Puis le manteau.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2442,7 +2530,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2610,7 +2698,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2638,7 +2729,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans la cuisine. Un cube jaune attrape le soleil du matin. Les cubes restent près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2778,7 +2869,30 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|Un cube jaune attrape le soleil du matin.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2806,7 +2920,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2946,7 +3060,14 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2974,7 +3095,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans la cuisine. Un cube est tiède, près d'une miette. Les cubes restent près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3114,7 +3235,30 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|Un cube est tiède, près d'une miette.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3142,7 +3286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3282,7 +3426,14 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3310,7 +3461,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans la cuisine. Un cube brille sous la petite lampe. Les cubes restent près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3450,7 +3601,30 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|Un cube brille sous la petite lampe.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3478,7 +3652,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3618,7 +3792,14 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3646,7 +3827,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Dans la cuisine, le livre est près de la miette. Une page est un peu rêche. Il y a un pain, maman ! Comme le nôtre, tout à l'heure. On regarde ensemble. Le manteau jaune reste sur la chaise. Quand on sort, on le prend. En rentrant, on le raccroche. Je m'en souviens. Bravo, Sarah. Sarah pose encore un cube, tout lent. Le carrelage est froid sous le pied. Tu as fini ce jeu ? Encore un peu. D'accord. Puis le manteau.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3786,7 +3967,21 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, le livre est près de la miette.
+narrateur|Une page est un peu rêche.
+enfant-f|Il y a un pain, maman !
+maman|Comme le nôtre, tout à l'heure.
+papa|On regarde ensemble.
+narrateur|Le manteau jaune reste sur la chaise.
+papa|Quand on sort, on le prend.
+maman|En rentrant, on le raccroche.
+enfant-f|Je m'en souviens.
+papa|Bravo, Sarah.
+narrateur|Sarah pose encore un cube, tout lent.
+narrateur|Le carrelage est froid sous le pied.
+maman|Tu as fini ce jeu ?
+enfant-f|Encore un peu.
+papa|D'accord. Puis le manteau.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3814,7 +4009,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3982,7 +4177,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4010,7 +4208,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans la cuisine. Une page sent encore le pain grillé. Le livre reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4150,7 +4348,30 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|Une page sent encore le pain grillé.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4178,7 +4399,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4318,7 +4539,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4346,7 +4574,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans la cuisine. Une page est un peu chaude, sous la main. Le livre reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4486,7 +4714,30 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|Une page est un peu chaude, sous la main.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4514,7 +4765,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4654,7 +4905,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4682,7 +4940,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans la cuisine. Une page fait un bruit tout fin. Le livre reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4822,7 +5080,30 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|Une page fait un bruit tout fin.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4850,7 +5131,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4990,7 +5271,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5018,7 +5306,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>Dans la cuisine, la dînette cliquette. La petite tasse est près de l'évier. Un thé, maman ? Un thé pour les poupées. Tout doux, la tasse. Le manteau jaune reste sur la chaise. Quand on sort, on le prend. En rentrant, on le raccroche. Je m'en souviens. Bravo, Sarah. Sarah pose encore un cube, tout lent. Le carrelage est froid sous le pied. Tu as fini ce jeu ? Encore un peu. D'accord. Puis le manteau.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5158,7 +5446,21 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, la dînette cliquette.
+narrateur|La petite tasse est près de l'évier.
+enfant-f|Un thé, maman ?
+maman|Un thé pour les poupées.
+papa|Tout doux, la tasse.
+narrateur|Le manteau jaune reste sur la chaise.
+papa|Quand on sort, on le prend.
+maman|En rentrant, on le raccroche.
+enfant-f|Je m'en souviens.
+papa|Bravo, Sarah.
+narrateur|Sarah pose encore un cube, tout lent.
+narrateur|Le carrelage est froid sous le pied.
+maman|Tu as fini ce jeu ?
+enfant-f|Encore un peu.
+papa|D'accord. Puis le manteau.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5186,7 +5488,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5354,7 +5656,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5382,7 +5687,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans la cuisine. La tasse cliquette près de la miette. La dînette reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5522,7 +5827,30 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|La tasse cliquette près de la miette.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5550,7 +5878,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5690,7 +6018,14 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5718,7 +6053,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans la cuisine. La tasse est tiède, comme la table. La dînette reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5858,7 +6193,30 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|La tasse est tiède, comme la table.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5886,7 +6244,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6026,7 +6384,14 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6054,7 +6419,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans la cuisine. La tasse a un reflet de lampe. La dînette reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Le manteau jaune. Sarah prend le manteau sur la chaise. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent un moment dehors. Puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau sur la chaise. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6194,7 +6559,30 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans la cuisine.
+narrateur|La tasse a un reflet de lampe.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah prend le manteau sur la chaise.
+narrateur|Elle glisse un bras, puis l'autre.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils passent un moment dehors.
+narrateur|Puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau sur la chaise.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6222,7 +6610,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le carrelage est sec, maintenant. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6362,7 +6750,14 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le carrelage est sec, maintenant.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6390,7 +6785,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers le jardin. L'air est frais, près de la porte. L'herbe est un peu mouillée. Une feuille brille, toute lisse. Le manteau jaune attend au crochet. Avant de sortir, Sarah. On prend le manteau. Je le prends. Sarah prend le manteau jaune. Elle glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Ils passent la porte. Le tuyau d'arrosage est froid. Il est froid, papa. Oui. Comme l'herbe. En rentrant, on raccroche le manteau. Une goutte tombe encore de la gouttière. Sarah marche dans l'herbe courte.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6530,8 +6925,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Sarah va vers le jardin.
+narrateur|L'air est frais, près de la porte.
+narrateur|L'herbe est un peu mouillée.
+narrateur|Une feuille brille, toute lisse.
+narrateur|Le manteau jaune attend au crochet.
+papa|Avant de sortir, Sarah.
+papa|On prend le manteau.
+enfant-f|Je le prends.
+narrateur|Sarah prend le manteau jaune.
+narrateur|Elle glisse un bras, puis l'autre.
+maman|Bravo. Tu as pris ton manteau.
+narrateur|Ils passent la porte.
+narrateur|Le tuyau d'arrosage est froid.
+enfant-f|Il est froid, papa.
+papa|Oui. Comme l'herbe.
+maman|En rentrant, on raccroche le manteau.
+narrateur|Une goutte tombe encore de la gouttière.
+narrateur|Sarah marche dans l'herbe courte.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6559,7 +6970,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Sarah va au jardin. Avant de sortir, elle prend quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6719,7 +7130,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Sarah va au jardin.
+papa|Avant de sortir, elle prend quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6747,7 +7159,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On prend le manteau, avant de sortir. Le manteau jaune est au crochet. Bravo, Sarah. Tu t'es souvenue. En rentrant, on le raccroche. Je le pose. Oui. C'est du bon travail. L'herbe brille un peu. Une feuille tremble.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6891,7 +7303,16 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+narrateur|On prend le manteau, avant de sortir.
+narrateur|Le manteau jaune est au crochet.
+maman|Bravo, Sarah.
+maman|Tu t'es souvenue.
+papa|En rentrant, on le raccroche.
+enfant-f|Je le pose.
+papa|Oui. C'est du bon travail.
+narrateur|L'herbe brille un peu.
+narrateur|Une feuille tremble.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6919,7 +7340,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Sarah peut encore jouer, dans le jardin. Les cubes, le livre, ou la dînette ? Tu choisis. Le manteau attend, tout près.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7087,7 +7508,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Sarah peut encore jouer, dans le jardin.
+maman|Les cubes, le livre, ou la dînette ?
+papa|Tu choisis.
+papa|Le manteau attend, tout près.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7115,7 +7539,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>Dans le jardin, les cubes sont dans l'herbe. L'herbe est un peu mouillée. Ils sont froids. Oui. Comme le tuyau. On pose un mur, tout bas. Le manteau jaune est sur Sarah. Il est un peu épais, dehors. Tu l'as pris avant de sortir. En rentrant, on le raccroche. Au crochet. Oui. Bravo. Une goutte tombe de la gouttière. Sarah touche encore une feuille. Tu as fini ce jeu ? Presque. L'herbe colle un peu aux cubes.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7255,7 +7679,22 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, les cubes sont dans l'herbe.
+narrateur|L'herbe est un peu mouillée.
+enfant-f|Ils sont froids.
+papa|Oui. Comme le tuyau.
+maman|On pose un mur, tout bas.
+narrateur|Le manteau jaune est sur Sarah.
+narrateur|Il est un peu épais, dehors.
+maman|Tu l'as pris avant de sortir.
+papa|En rentrant, on le raccroche.
+enfant-f|Au crochet.
+maman|Oui. Bravo.
+narrateur|Une goutte tombe de la gouttière.
+narrateur|Sarah touche encore une feuille.
+papa|Tu as fini ce jeu ?
+enfant-f|Presque.
+narrateur|L'herbe colle un peu aux cubes.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7283,7 +7722,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7451,7 +7890,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7479,7 +7921,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans le jardin. Un cube a une goutte d'herbe dessus. Les cubes restent près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7619,7 +8061,29 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans le jardin.
+narrateur|Un cube a une goutte d'herbe dessus.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7647,7 +8111,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7787,7 +8251,14 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7815,7 +8286,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans le jardin. Un cube sent l'herbe chaude, un peu. Les cubes restent près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7955,7 +8426,29 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans le jardin.
+narrateur|Un cube sent l'herbe chaude, un peu.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7983,7 +8476,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8123,7 +8616,14 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8151,7 +8651,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans le jardin. Un cube est froid, comme la terre. Les cubes restent près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8291,7 +8791,29 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans le jardin.
+narrateur|Un cube est froid, comme la terre.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8319,7 +8841,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8459,7 +8981,14 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8487,7 +9016,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Dans le jardin, le livre a une feuille dessus. La feuille vraie est lisse. Elle est verte, papa. Oui. On la laisse sur le livre ? On la pose à côté. Le manteau jaune est sur Sarah. Il est un peu épais, dehors. Tu l'as pris avant de sortir. En rentrant, on le raccroche. Au crochet. Oui. Bravo. Une goutte tombe de la gouttière. Sarah touche encore une feuille. Tu as fini ce jeu ? Presque. L'herbe colle un peu aux cubes.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8627,7 +9156,22 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, le livre a une feuille dessus.
+narrateur|La feuille vraie est lisse.
+enfant-f|Elle est verte, papa.
+papa|Oui. On la laisse sur le livre ?
+maman|On la pose à côté.
+narrateur|Le manteau jaune est sur Sarah.
+narrateur|Il est un peu épais, dehors.
+maman|Tu l'as pris avant de sortir.
+papa|En rentrant, on le raccroche.
+enfant-f|Au crochet.
+maman|Oui. Bravo.
+narrateur|Une goutte tombe de la gouttière.
+narrateur|Sarah touche encore une feuille.
+papa|Tu as fini ce jeu ?
+enfant-f|Presque.
+narrateur|L'herbe colle un peu aux cubes.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8655,7 +9199,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8823,7 +9367,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8851,7 +9398,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans le jardin. Une feuille vraie s'est posée sur le livre. Le livre reste près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8991,7 +9538,29 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans le jardin.
+narrateur|Une feuille vraie s'est posée sur le livre.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9019,7 +9588,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9159,7 +9728,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9187,7 +9763,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans le jardin. Le livre a une odeur de jardin tiède. Le livre reste près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9327,7 +9903,29 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans le jardin.
+narrateur|Le livre a une odeur de jardin tiède.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9355,7 +9953,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9495,7 +10093,14 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9523,7 +10128,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans le jardin. Le livre a un coin un peu humide. Le livre reste près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9663,7 +10268,29 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans le jardin.
+narrateur|Le livre a un coin un peu humide.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9691,7 +10318,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9831,7 +10458,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9859,7 +10493,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>Dans le jardin, la dînette est au soleil. La tasse est un peu tiède. Un goûter dehors. Un goûter de jardin. La tasse sonne tout bas. Le manteau jaune est sur Sarah. Il est un peu épais, dehors. Tu l'as pris avant de sortir. En rentrant, on le raccroche. Au crochet. Oui. Bravo. Une goutte tombe de la gouttière. Sarah touche encore une feuille. Tu as fini ce jeu ? Presque. L'herbe colle un peu aux cubes.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9999,7 +10633,22 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, la dînette est au soleil.
+narrateur|La tasse est un peu tiède.
+enfant-f|Un goûter dehors.
+maman|Un goûter de jardin.
+papa|La tasse sonne tout bas.
+narrateur|Le manteau jaune est sur Sarah.
+narrateur|Il est un peu épais, dehors.
+maman|Tu l'as pris avant de sortir.
+papa|En rentrant, on le raccroche.
+enfant-f|Au crochet.
+maman|Oui. Bravo.
+narrateur|Une goutte tombe de la gouttière.
+narrateur|Sarah touche encore une feuille.
+papa|Tu as fini ce jeu ?
+enfant-f|Presque.
+narrateur|L'herbe colle un peu aux cubes.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10027,7 +10676,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10195,7 +10844,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10223,7 +10875,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans le jardin. La tasse a une paillette de rosée. La dînette reste près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10363,7 +11015,29 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans le jardin.
+narrateur|La tasse a une paillette de rosée.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10391,7 +11065,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10531,7 +11205,14 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10559,7 +11240,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans le jardin. La tasse est chaude, côté soleil. La dînette reste près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10699,7 +11380,29 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans le jardin.
+narrateur|La tasse est chaude, côté soleil.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10727,7 +11430,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10867,7 +11570,14 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10895,7 +11605,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans le jardin. La tasse sonne tout bas, dans l'air frais. La dînette reste près d'elle. C'est l'heure de rentrer. En rentrant, on raccroche le manteau. Le manteau jaune. Sarah a encore le manteau sur elle. Elle est rentrée par la porte. Tu l'as pris avant de sortir. Sarah retire le manteau, tout doux. Elle le raccroche au crochet. Bravo. Il est à sa place. Le crochet fait un petit toc. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11035,7 +11745,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans le jardin.
+narrateur|La tasse sonne tout bas, dans l'air frais.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de rentrer.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Le manteau jaune.
+narrateur|Sarah a encore le manteau sur elle.
+narrateur|Elle est rentrée par la porte.
+papa|Tu l'as pris avant de sortir.
+narrateur|Sarah retire le manteau, tout doux.
+narrateur|Elle le raccroche au crochet.
+maman|Bravo. Il est à sa place.
+narrateur|Le crochet fait un petit toc.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11063,7 +11795,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Une feuille reste collée au tuyau. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11203,7 +11935,14 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Une feuille reste collée au tuyau.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11231,7 +11970,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers la chambre. Le tapis de laine est doux. Un rayon pose un carré au sol. La couverture est un peu froissée. Le manteau jaune est sur le lit. On va sortir un moment. Avant de sortir, on prend le manteau. Il est sur le lit. Sarah prend le manteau. Le bouton argenté est froid. Bravo, Sarah. Tu as pris ton manteau. En rentrant, on le raccroche. Près de la fenêtre ? Oui. Au crochet. Un oreiller sent encore le sommeil. Sarah passe près de la vitre. Le trait d'argent du limaçon brille.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11371,8 +12110,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Sarah va vers la chambre.
+narrateur|Le tapis de laine est doux.
+narrateur|Un rayon pose un carré au sol.
+narrateur|La couverture est un peu froissée.
+narrateur|Le manteau jaune est sur le lit.
+maman|On va sortir un moment.
+papa|Avant de sortir, on prend le manteau.
+enfant-f|Il est sur le lit.
+narrateur|Sarah prend le manteau.
+narrateur|Le bouton argenté est froid.
+maman|Bravo, Sarah.
+maman|Tu as pris ton manteau.
+papa|En rentrant, on le raccroche.
+enfant-f|Près de la fenêtre ?
+papa|Oui. Au crochet.
+narrateur|Un oreiller sent encore le sommeil.
+narrateur|Sarah passe près de la vitre.
+narrateur|Le trait d'argent du limaçon brille.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11400,7 +12155,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Sarah est dans la chambre. Avant de sortir, elle prend quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11560,7 +12315,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Sarah est dans la chambre.
+maman|Avant de sortir, elle prend quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11588,7 +12344,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On prend le manteau, avant de sortir. Le manteau jaune était sur le lit. Bravo, Sarah. Tu as pris ton manteau. En rentrant, on le raccroche. Au crochet. Oui. On continue ? Oui, maman. Le tapis reste doux sous le pied.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11732,7 +12488,16 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Sara respire. Sara retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+narrateur|On prend le manteau, avant de sortir.
+narrateur|Le manteau jaune était sur le lit.
+papa|Bravo, Sarah.
+papa|Tu as pris ton manteau.
+maman|En rentrant, on le raccroche.
+enfant-f|Au crochet.
+maman|Oui. On continue ?
+enfant-f|Oui, maman.
+narrateur|Le tapis reste doux sous le pied.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11760,7 +12525,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Sarah peut encore jouer, dans la chambre. Les cubes, le livre, ou la dînette ? Tu choisis. Le manteau attend, tout près.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11928,7 +12693,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Sarah peut encore jouer, dans la chambre.
+maman|Les cubes, le livre, ou la dînette ?
+papa|Tu choisis.
+papa|Le manteau attend, tout près.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11956,7 +12724,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>Dans la chambre, les cubes sont sur le tapis. Le tapis de laine est doux. Une tour, maman. Une tour, tout doux. Le tapis étouffe le toc. Le manteau jaune attend près du lit. Avant de sortir, on le prend. En rentrant, on le raccroche. Près de la fenêtre. Oui. Au crochet. Bravo, Sarah. Sarah lisse encore la couverture. Tu as fini ce jeu ? Oui, bientôt. Le rayon a bougé sur le tapis.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12096,7 +12864,21 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, les cubes sont sur le tapis.
+narrateur|Le tapis de laine est doux.
+enfant-f|Une tour, maman.
+maman|Une tour, tout doux.
+papa|Le tapis étouffe le toc.
+narrateur|Le manteau jaune attend près du lit.
+papa|Avant de sortir, on le prend.
+maman|En rentrant, on le raccroche.
+enfant-f|Près de la fenêtre.
+papa|Oui. Au crochet.
+maman|Bravo, Sarah.
+narrateur|Sarah lisse encore la couverture.
+maman|Tu as fini ce jeu ?
+enfant-f|Oui, bientôt.
+narrateur|Le rayon a bougé sur le tapis.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12124,7 +12906,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12292,7 +13074,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12320,7 +13105,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans la chambre. Un cube roule sur le tapis de laine. Les cubes restent près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12460,7 +13245,30 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans la chambre.
+narrateur|Un cube roule sur le tapis de laine.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12488,7 +13296,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12628,7 +13436,14 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12656,7 +13471,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans la chambre. Un cube est doux de chaleur, près du lit. Les cubes restent près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12796,7 +13611,30 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans la chambre.
+narrateur|Un cube est doux de chaleur, près du lit.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12824,7 +13662,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12964,7 +13802,14 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12992,7 +13837,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans la chambre. Un cube fait une ombre longue, le soir. Les cubes restent près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13132,7 +13977,30 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans la chambre.
+narrateur|Un cube fait une ombre longue, le soir.
+narrateur|Les cubes restent près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13160,7 +14028,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13300,7 +14168,14 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13328,7 +14203,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Dans la chambre, le livre est sur le lit. La couverture est un peu froissée. Une histoire, papa. On en lit une page. Une page, puis on sort. Le manteau jaune attend près du lit. Avant de sortir, on le prend. En rentrant, on le raccroche. Près de la fenêtre. Oui. Au crochet. Bravo, Sarah. Sarah lisse encore la couverture. Tu as fini ce jeu ? Oui, bientôt. Le rayon a bougé sur le tapis.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13468,7 +14343,21 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, le livre est sur le lit.
+narrateur|La couverture est un peu froissée.
+enfant-f|Une histoire, papa.
+papa|On en lit une page.
+maman|Une page, puis on sort.
+narrateur|Le manteau jaune attend près du lit.
+papa|Avant de sortir, on le prend.
+maman|En rentrant, on le raccroche.
+enfant-f|Près de la fenêtre.
+papa|Oui. Au crochet.
+maman|Bravo, Sarah.
+narrateur|Sarah lisse encore la couverture.
+maman|Tu as fini ce jeu ?
+enfant-f|Oui, bientôt.
+narrateur|Le rayon a bougé sur le tapis.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13496,7 +14385,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13664,7 +14553,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13692,7 +14584,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans la chambre. Le livre est ouvert sur la couverture. Le livre reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13832,7 +14724,30 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans la chambre.
+narrateur|Le livre est ouvert sur la couverture.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13860,7 +14775,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14000,7 +14915,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14028,7 +14950,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans la chambre. Le livre a gardé un pli de sieste. Le livre reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14168,7 +15090,30 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans la chambre.
+narrateur|Le livre a gardé un pli de sieste.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14196,7 +15141,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14336,7 +15281,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14364,7 +15316,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans la chambre. Le livre est près de la petite lampe. Le livre reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14504,7 +15456,30 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans la chambre.
+narrateur|Le livre est près de la petite lampe.
+narrateur|Le livre reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14532,7 +15507,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14672,7 +15647,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14700,7 +15682,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>Dans la chambre, la dînette est près de l'oreiller. La tasse a un rond de lumière. Le dîner des poupées. Un tout petit dîner. La tasse cliquette, tout bas. Le manteau jaune attend près du lit. Avant de sortir, on le prend. En rentrant, on le raccroche. Près de la fenêtre. Oui. Au crochet. Bravo, Sarah. Sarah lisse encore la couverture. Tu as fini ce jeu ? Oui, bientôt. Le rayon a bougé sur le tapis.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14840,7 +15822,21 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Sara répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, la dînette est près de l'oreiller.
+narrateur|La tasse a un rond de lumière.
+enfant-f|Le dîner des poupées.
+maman|Un tout petit dîner.
+papa|La tasse cliquette, tout bas.
+narrateur|Le manteau jaune attend près du lit.
+papa|Avant de sortir, on le prend.
+maman|En rentrant, on le raccroche.
+enfant-f|Près de la fenêtre.
+papa|Oui. Au crochet.
+maman|Bravo, Sarah.
+narrateur|Sarah lisse encore la couverture.
+maman|Tu as fini ce jeu ?
+enfant-f|Oui, bientôt.
+narrateur|Le rayon a bougé sur le tapis.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14868,7 +15864,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut sortir à plusieurs heures. Le matin, après la sieste, ou le soir ? Avant de sortir, on prend le manteau. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15036,7 +16032,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut sortir à plusieurs heures.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Avant de sortir, on prend le manteau.
+maman|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15064,7 +16063,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le matin, tout neuf. La lumière est blanche, très claire. Un oiseau chante une fois, dehors. Sarah est encore dans la chambre. La tasse attend près de l'oreiller clair. La dînette reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. La gouttière est calme, ce matin. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15204,7 +16203,30 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin, tout neuf.
+narrateur|La lumière est blanche, très claire.
+narrateur|Un oiseau chante une fois, dehors.
+narrateur|Sarah est encore dans la chambre.
+narrateur|La tasse attend près de l'oreiller clair.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La gouttière est calme, ce matin.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15232,7 +16254,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Le matin est calme, près de la vitre. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15372,7 +16394,14 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Le matin est calme, près de la vitre.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15400,7 +16429,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Sarah a une joue un peu marquée. Les volets laissent une bande d'ombre. Sarah est encore dans la chambre. La tasse est tiède, comme la joue. La dînette reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le pain grillé n'est plus chaud. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15540,7 +16569,30 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Sarah a une joue un peu marquée.
+narrateur|Les volets laissent une bande d'ombre.
+narrateur|Sarah est encore dans la chambre.
+narrateur|La tasse est tiède, comme la joue.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pain grillé n'est plus chaud.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15568,7 +16620,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Après la sieste, le manteau est à sa place. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15708,7 +16760,14 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Après la sieste, le manteau est à sa place.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15736,7 +16795,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>C'est le soir, tout doux. Une petite lampe est allumée. Les chaussures font toc toc, au loin. Sarah est encore dans la chambre. La tasse a un rond de lumière jaune. La dînette reste près d'elle. C'est l'heure de sortir. Avant de sortir, on prend le manteau. Il est près du lit. Sarah prend le manteau sur le lit. Le bouton argenté est froid. Bravo. Tu as pris ton manteau. Ils descendent, puis ils rentrent. En rentrant, on le raccroche. Sarah raccroche le manteau au crochet. Le crochet est près de la fenêtre. Tu as fini de le poser ? Oui, papa. Bravo. Tu as fait du bon travail. Le limaçon a quitté la vitre. Merci, maman. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15876,7 +16935,30 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Sara a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Sara a entendu : manteau, sortir, rentrer. Sara dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir, tout doux.
+narrateur|Une petite lampe est allumée.
+narrateur|Les chaussures font toc toc, au loin.
+narrateur|Sarah est encore dans la chambre.
+narrateur|La tasse a un rond de lumière jaune.
+narrateur|La dînette reste près d'elle.
+papa|C'est l'heure de sortir.
+maman|Avant de sortir, on prend le manteau.
+enfant-f|Il est près du lit.
+narrateur|Sarah prend le manteau sur le lit.
+narrateur|Le bouton argenté est froid.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils descendent, puis ils rentrent.
+maman|En rentrant, on le raccroche.
+narrateur|Sarah raccroche le manteau au crochet.
+narrateur|Le crochet est près de la fenêtre.
+papa|Tu as fini de le poser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le limaçon a quitté la vitre.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15904,7 +16986,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Sarah. Tu as fait du bon travail. Tu as pris le manteau. Tu l'as raccroché en rentrant. Le tapis de laine est calme. Le soir, la petite lampe veille. Le limaçon est parti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16044,7 +17126,14 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+maman|Tu as pris le manteau.
+maman|Tu l'as raccroché en rentrant.
+narrateur|Le tapis de laine est calme.
+narrateur|Le soir, la petite lampe veille.
+enfant-f|Le limaçon est parti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16066,7 +17155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16104,6 +17193,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
